--- a/stage4_competency_graph/output/08_图谱关系人工审查清单.xlsx
+++ b/stage4_competency_graph/output/08_图谱关系人工审查清单.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工审查" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'人工审查'!$A$1:$F$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'人工审查'!$A$1:$L$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -434,6 +434,12 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="54" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +473,36 @@
           <t>state</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>review_category</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>classification_reason</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>original_review_id</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>handling_suggestion</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>impact_scope</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>human_confirmation_required</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +535,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Q:R03:001</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>建议保留；SELECT结构对应执行查询与提取结果；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R03:001</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -531,6 +595,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Q:R03:002</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>建议保留；字段别名与表达式对应取数结果表达；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R03:002</t>
+        </is>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +655,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Q:R03:003</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>建议保留；P05 WHERE条件过滤对应取数筛选；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R03:003</t>
+        </is>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,6 +715,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Q:R03:004</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>建议保留；排序可组织查询输出；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R03:004</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -627,6 +775,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Q:R03:005</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>建议保留；LIMIT控制返回数据范围；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R03:005</t>
+        </is>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -651,13 +827,41 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只在问题记录和修正规则已给定时支持UPDATE实施；不涵盖问题识别、清洗规则设计及清洗结果验证。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Q:R03:006</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；仅当清洗规则涉及记录值修正时UPDATE提供实现方法；只在问题记录和修正规则已给定时支持UPDATE实施；不涵盖问题识别、清洗规则设计及清洗结果验证。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R03:006</t>
+        </is>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -683,13 +887,41 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只支持给定清洗条件的记录定位；不证明完整清洗流程、异常判断及前后质量验证已安排。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Q:R03:007</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；WHERE可表达筛选条件，但业务清洗规则本身不由语法给出；只支持给定清洗条件的记录定位；不证明完整清洗流程、异常判断及前后质量验证已安排。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R03:007</t>
+        </is>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -723,6 +955,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Q:R03:008</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>建议保留；使用CTB001独立备份实验接口，对应备份操作目标；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。同一组合句分别标行为，不合并能力，不推导教学先修。</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R03:008</t>
+        </is>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -755,6 +1015,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Q:R03:009</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>建议保留；使用CTB002独立恢复实验接口，对应恢复操作目标；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。同一组合句分别标行为，不合并能力，不推导教学先修。</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R03:009</t>
+        </is>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -787,6 +1075,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Q:R03:010</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>建议保留；索引类型只支持优化中的索引路线，不涵盖全部性能问题；只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R03:010</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -819,6 +1135,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Q:R03:011</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>建议保留；有无索引效果比较可为局部性能改进提供观察依据；只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R03:011</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -851,6 +1195,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Q:R03:012</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>建议保留；UPDATE作用对象是记录值，不是表结构；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R03:012</t>
+        </is>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -883,6 +1255,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Q:R03:013</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>建议保留；P04 WHERE与UPDATE组合支持精确更新；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R03:013</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -915,6 +1315,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Q:R03:014</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>建议保留；概念模型帮助把业务需求表达为结构设计输入；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R03:014</t>
+        </is>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -947,6 +1375,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Q:R03:015</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>建议保留；关系模式转换直接服务表及关联结构设计；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R03:015</t>
+        </is>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -979,6 +1435,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Q:R03:016</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>建议保留；范式知识为结构合理性分析提供理论依据；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R03:016</t>
+        </is>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1011,6 +1495,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Q:R03:017</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>建议保留；对象属性联系是表字段及关联设计的基础；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R03:017</t>
+        </is>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1035,13 +1547,41 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>第5页明确主键作用及语法；仅在关系表标识方案已确定时支持实现表达，不能把约束SQL实现等同完整模式设计。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Q:R03:018</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；主键在需要唯一标识时支撑表结构表达；第5页明确主键作用及语法；仅在关系表标识方案已确定时支持实现表达，不能把约束SQL实现等同完整模式设计。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R03:018</t>
+        </is>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1067,13 +1607,41 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>第5页明确外键作用及语法；仅在参照关系方案已确定时支持实现，不替代实体关系识别与完整结构设计。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Q:R03:019</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；外键在参照关系方案中支持关联结构；第5页明确外键作用及语法；仅在参照关系方案已确定时支持实现，不替代实体关系识别与完整结构设计。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>R03:019</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1107,6 +1675,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Q:R03:020</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>建议保留；INSERT语法直接对应向指定表写入新增记录；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>R03:020</t>
+        </is>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1139,6 +1735,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Q:R03:021</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>建议保留；类型及适用场景帮助选择索引；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>R03:021</t>
+        </is>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1163,13 +1787,41 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只支持选定索引方案的创建实施，不证明能根据查询需求选择索引或验证调整收益。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Q:R03:022</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；CREATE INDEX为选定索引方案提供操作方法；只支持选定索引方案的创建实施，不证明能根据查询需求选择索引或验证调整收益。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>R03:022</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1195,13 +1847,41 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只支持既定方案的索引添加实施；索引选择、负面影响分析及迭代调整仍需其他依据。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Q:R03:023</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；该操作用于索引调整方案的实施；只支持既定方案的索引添加实施；索引选择、负面影响分析及迭代调整仍需其他依据。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>R03:023</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1227,13 +1907,41 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>只在建表时定义索引的方案下成立，不代表能调整已有库索引，也不证明完整选择与调整能力。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Q:R03:024</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；仅在建表方案中通过约束或索引定义实施索引设计；只在建表时定义索引的方案下成立，不代表能调整已有库索引，也不证明完整选择与调整能力。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>R03:024</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1259,13 +1967,41 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>删除/维护索引操作不等于诊断索引问题；具体变更理由与效果核查仍未由本知识单独覆盖。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Q:R03:025</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；删除维护可实施调整，但还需判断依据；删除/维护索引操作不等于诊断索引问题；具体变更理由与效果核查仍未由本知识单独覆盖。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>R03:025</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1291,13 +2027,41 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>第11页仅明示有无索引查询效果对比；K3指与其他索引知识组合的观察线索，不证明完整方案选择及迭代调整闭环。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Q:R03:026</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；效果对比与选择调整结合，形成结果核对线索；第11页仅明示有无索引查询效果对比；K3指与其他索引知识组合的观察线索，不证明完整方案选择及迭代调整闭环。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>R03:026</t>
+        </is>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1331,6 +2095,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Q:R03:027</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>建议保留；聚合函数对应数据统计计算；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>R03:027</t>
+        </is>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1363,6 +2155,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Q:R03:028</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>建议保留；GROUP BY直接对应分组聚合的分组行为；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>R03:028</t>
+        </is>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1395,6 +2215,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Q:R03:029</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>建议保留；HAVING与分组聚合组合处理汇总结果；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>R03:029</t>
+        </is>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1419,13 +2267,41 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>只在所述技术方案或规则已确定时适用；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>在已有质量检查条件的前提下，支持筛选待核查记录；不涵盖质量维度定义、规则制定、异常原因判断和完整核查结果验证。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Q:R03:030</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；WHERE可表达已给定质量条件；未证明课程有完整数据质量核查任务；在已有质量检查条件的前提下，支持筛选待核查记录；不涵盖质量维度定义、规则制定、异常原因判断和完整核查结果验证。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>R03:030</t>
+        </is>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1459,6 +2335,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Q:R03:031</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>建议保留；ALTER TABLE技术对象是表结构，区别于UPDATE记录值；仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>R03:031</t>
+        </is>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1483,13 +2387,41 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>仅对应内外连接语法及关联条件；完整业务语义、重复行及结果正确性仍需任务情境核查。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Q:R03:032</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；内外连接原理与语法直接对应多表连接查询；仅对应内外连接语法及关联条件；完整业务语义、重复行及结果正确性仍需任务情境核查。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>R03:032</t>
+        </is>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1515,13 +2447,41 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>一般SELECT只提供表达框架，不自动支持连接条件设计或多表结果核验。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Q:R03:033</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>建议调整关系说明或适用边界；SELECT为连接查询提供表达框架，但一般SELECT不能完整覆盖JOIN；一般SELECT只提供表达框架，不自动支持连接条件设计或多表结果核验。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>R03:033</t>
+        </is>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1542,18 +2502,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>外键知识帮助理解关联字段；连接并不要求存在外键约束</t>
+          <t>第5页外键约束知识仅在参照关系解释场景中帮助理解关联字段；JOIN本身不依赖外键定义，因此采用条件性K4而非一般基础前提。</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>仅为具体技术行为支撑候选；未证明完整岗位能力已培养、学生达标或已有正式考核。</t>
+          <t>外键知识仅在解释既有参照关系时提供条件性理解线索；SQL JOIN不要求已定义外键约束，不是必要前提。 本条仍为跨体系研究推断，待人工确认。</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>待研究者审查</t>
         </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Q:R03:034</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>建议调整支撑类型；第5页外键约束知识仅在参照关系解释场景中帮助理解关联字段；JOIN本身不依赖外键定义，因此采用条件性K4而非一般基础前提。；外键知识仅在解释既有参照关系时提供条件性理解线索；SQL JOIN不要求已定义外键约束，不是必要前提。 本条仍为跨体系研究推断，待人工确认。</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>R03:034</t>
+        </is>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1587,6 +2575,34 @@
           <t>待研究者审查，未经专家确认</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Q:FR-L006</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>R09:FR-L006</t>
+        </is>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1619,6 +2635,34 @@
           <t>待研究者审查，未经专家确认</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>关系类型、方向及默认边集判定</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Q:FR-L007</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>R09:FR-L007</t>
+        </is>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1651,6 +2695,34 @@
           <t>待研究者审查，未经专家确认</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>关系类型、方向及默认边集判定</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Q:FR-L008</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>R09:FR-L008</t>
+        </is>
+      </c>
+      <c r="L38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1683,6 +2755,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>COURSE:CQ001</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PDF第13页</t>
+        </is>
+      </c>
+      <c r="L39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1715,6 +2815,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COURSE:CQ002</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PT01—PT03与P01—P08</t>
+        </is>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1747,6 +2875,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COURSE:CQ003</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>PT02</t>
+        </is>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1779,6 +2935,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>COURSE:CQ004</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>课程考核</t>
+        </is>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1811,6 +2995,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COURSE:CQ005</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>目标与项目</t>
+        </is>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1843,6 +3055,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>术语及课程知识技术边界</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COURSE:CQ006</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1875,6 +3115,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>COURSE:CQ007</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1907,6 +3175,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>COURSE:CQ008</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1939,6 +3235,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>术语及课程知识技术边界</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>COURSE:CQ009</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1971,6 +3295,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COURSE:CQ010</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>学习成果</t>
+        </is>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2003,6 +3355,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>术语及课程知识技术边界</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>COURSE:CQ011</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>知识规范化</t>
+        </is>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2035,6 +3415,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>课程原始文本或任务安排限制</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>COURSE:CQ012</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>课程定位/页眉</t>
+        </is>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2067,6 +3475,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NO:DB009</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>DB009</t>
+        </is>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2099,6 +3535,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>NO:DB010</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>DB010</t>
+        </is>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2131,6 +3595,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>NO:DB014</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>DB014</t>
+        </is>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2163,6 +3655,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>涉及技术行为与完整能力边界</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>NO:DB015</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>DB015</t>
+        </is>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2195,6 +3715,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q001</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>DB001</t>
+        </is>
+      </c>
+      <c r="L55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2227,6 +3775,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q002</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>DB017</t>
+        </is>
+      </c>
+      <c r="L56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2259,6 +3835,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q003</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>DB005</t>
+        </is>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2291,6 +3895,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q004</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>DB011</t>
+        </is>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2323,6 +3955,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q005</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>DB006</t>
+        </is>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2355,6 +4015,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q006</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>DB016</t>
+        </is>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2387,6 +4075,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q007</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>DB007</t>
+        </is>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2419,6 +4135,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q008</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DB008</t>
+        </is>
+      </c>
+      <c r="L62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2451,6 +4195,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q009</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>DB009</t>
+        </is>
+      </c>
+      <c r="L63" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2483,6 +4255,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q010</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>DB010</t>
+        </is>
+      </c>
+      <c r="L64" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2515,6 +4315,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q011</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>DB012</t>
+        </is>
+      </c>
+      <c r="L65" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2547,6 +4375,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q012</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>DB013</t>
+        </is>
+      </c>
+      <c r="L66" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2579,6 +4435,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q013</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>DB014</t>
+        </is>
+      </c>
+      <c r="L67" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2611,6 +4495,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q014</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>DB015</t>
+        </is>
+      </c>
+      <c r="L68" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2643,6 +4555,34 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>关系类型、方向及默认边集判定</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q015</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>全部非层级关系</t>
+        </is>
+      </c>
+      <c r="L69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2675,9 +4615,37 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>继承岗位摘要明确程度、职责对象及证据来源限制</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>STAGE3:FR-Q016</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>保留问题，结合原依据逐项人工确认；测试通过不关闭研究问题</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>任务片段口径</t>
+        </is>
+      </c>
+      <c r="L70" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F70"/>
+  <autoFilter ref="A1:L70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>